--- a/Databases/Database3/Output/2018/db3_2018_clean.xlsx
+++ b/Databases/Database3/Output/2018/db3_2018_clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1098" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="235">
   <si>
     <t>unique_id</t>
   </si>
@@ -496,9 +496,6 @@
     <t>L9U LL=FG RL=_</t>
   </si>
   <si>
-    <t>0 banded birds then none readable</t>
-  </si>
-  <si>
     <t>Of//RB:S//b</t>
   </si>
   <si>
@@ -547,7 +544,7 @@
     <t>S/LY:bf/LG (bf = light blue flag, no code); reported directly to bander</t>
   </si>
   <si>
-    <t>this is just one says here. One individual. Band/flag code:1) YX6, color: green, position: upper left". The "O" is for an orange band on the right leg, position: upper right.</t>
+    <t>YX6, color: green, position: upper left". The "O" is for an orange band on the right leg, position: upper right.</t>
   </si>
   <si>
     <t>S//BK:Bf(C63)//YB</t>
@@ -592,7 +589,7 @@
     <t>FW[VA],_:S,_</t>
   </si>
   <si>
-    <t>4 Unbanded, 1) Banded - FK[UN], _ : S, _</t>
+    <t>Banded - FK[UN], _ : S, _</t>
   </si>
   <si>
     <t>Left leg: Orange flag, upper yellow band, lower green band. Right leg: Upper silver USFWS band, lower Yellow band</t>
@@ -1057,7 +1054,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R121"/>
+  <dimension ref="A1:R120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1151,16 +1148,16 @@
         <v>121</v>
       </c>
       <c r="O2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1198,16 +1195,16 @@
         <v>121</v>
       </c>
       <c r="O3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1248,16 +1245,16 @@
         <v>147</v>
       </c>
       <c r="O4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1298,16 +1295,16 @@
         <v>148</v>
       </c>
       <c r="O5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1348,16 +1345,16 @@
         <v>149</v>
       </c>
       <c r="O6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1398,16 +1395,16 @@
         <v>150</v>
       </c>
       <c r="O7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1448,16 +1445,16 @@
         <v>151</v>
       </c>
       <c r="O8" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1498,16 +1495,16 @@
         <v>152</v>
       </c>
       <c r="O9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1548,16 +1545,16 @@
         <v>153</v>
       </c>
       <c r="O10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1598,16 +1595,16 @@
         <v>154</v>
       </c>
       <c r="O11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1648,16 +1645,16 @@
         <v>155</v>
       </c>
       <c r="O12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P12" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1698,16 +1695,16 @@
         <v>156</v>
       </c>
       <c r="O13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1748,16 +1745,16 @@
         <v>157</v>
       </c>
       <c r="O14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1795,16 +1792,16 @@
         <v>121</v>
       </c>
       <c r="O15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1845,13 +1842,13 @@
         <v>158</v>
       </c>
       <c r="P16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1892,13 +1889,13 @@
         <v>159</v>
       </c>
       <c r="P17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1936,13 +1933,13 @@
         <v>122</v>
       </c>
       <c r="P18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1980,13 +1977,13 @@
         <v>123</v>
       </c>
       <c r="P19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2024,13 +2021,13 @@
         <v>123</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2068,13 +2065,13 @@
         <v>123</v>
       </c>
       <c r="P21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2112,13 +2109,13 @@
         <v>123</v>
       </c>
       <c r="P22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q22" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2156,13 +2153,13 @@
         <v>124</v>
       </c>
       <c r="P23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q23" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2200,13 +2197,13 @@
         <v>125</v>
       </c>
       <c r="P24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2244,16 +2241,16 @@
         <v>126</v>
       </c>
       <c r="O25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2282,7 +2279,7 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J26" t="s">
         <v>97</v>
@@ -2290,20 +2287,17 @@
       <c r="K26" t="s">
         <v>127</v>
       </c>
-      <c r="N26" t="s">
-        <v>160</v>
-      </c>
       <c r="O26" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q26" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2311,46 +2305,46 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>43136</v>
+        <v>43133</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F27">
-        <v>30.50892</v>
+        <v>29.99092</v>
       </c>
       <c r="G27">
-        <v>-81.4785</v>
+        <v>-85.502</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
       <c r="I27">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K27" t="s">
-        <v>127</v>
-      </c>
-      <c r="O27" t="s">
-        <v>224</v>
+        <v>128</v>
+      </c>
+      <c r="N27" t="s">
+        <v>160</v>
       </c>
       <c r="P27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q27" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2391,13 +2385,13 @@
         <v>161</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2438,13 +2432,13 @@
         <v>162</v>
       </c>
       <c r="P29" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2473,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" t="s">
         <v>98</v>
@@ -2481,17 +2475,14 @@
       <c r="K30" t="s">
         <v>128</v>
       </c>
-      <c r="N30" t="s">
-        <v>163</v>
-      </c>
       <c r="P30" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q30" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2502,40 +2493,43 @@
         <v>43133</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F31">
-        <v>29.99092</v>
+        <v>28.05099</v>
       </c>
       <c r="G31">
-        <v>-85.502</v>
+        <v>-82.8197</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K31" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="N31" t="s">
+        <v>163</v>
       </c>
       <c r="P31" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q31" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -2564,7 +2558,7 @@
         <v>2</v>
       </c>
       <c r="I32">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J32" t="s">
         <v>99</v>
@@ -2572,17 +2566,14 @@
       <c r="K32" t="s">
         <v>129</v>
       </c>
-      <c r="N32" t="s">
-        <v>164</v>
-      </c>
       <c r="P32" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q32" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2590,43 +2581,46 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>43133</v>
+        <v>43134</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F33">
-        <v>28.05099</v>
+        <v>25.70076</v>
       </c>
       <c r="G33">
-        <v>-82.8197</v>
+        <v>-80.1549</v>
       </c>
       <c r="H33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I33">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K33" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="N33" t="s">
+        <v>164</v>
       </c>
       <c r="P33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q33" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2667,13 +2661,13 @@
         <v>165</v>
       </c>
       <c r="P34" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q34" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R34" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2714,13 +2708,13 @@
         <v>166</v>
       </c>
       <c r="P35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q35" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2761,13 +2755,13 @@
         <v>167</v>
       </c>
       <c r="P36" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2808,13 +2802,13 @@
         <v>168</v>
       </c>
       <c r="P37" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q37" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2843,7 +2837,7 @@
         <v>1</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J38" t="s">
         <v>100</v>
@@ -2851,17 +2845,14 @@
       <c r="K38" t="s">
         <v>130</v>
       </c>
-      <c r="N38" t="s">
-        <v>169</v>
-      </c>
       <c r="P38" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q38" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2881,16 +2872,16 @@
         <v>68</v>
       </c>
       <c r="F39">
-        <v>25.70076</v>
+        <v>25.70171</v>
       </c>
       <c r="G39">
-        <v>-80.1549</v>
+        <v>-80.1544</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J39" t="s">
         <v>100</v>
@@ -2899,13 +2890,13 @@
         <v>130</v>
       </c>
       <c r="P39" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q39" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R39" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2913,43 +2904,46 @@
         <v>39</v>
       </c>
       <c r="B40" s="1">
-        <v>43134</v>
+        <v>43137</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F40">
-        <v>25.70171</v>
+        <v>29.071</v>
       </c>
       <c r="G40">
-        <v>-80.1544</v>
+        <v>-80.9263</v>
       </c>
       <c r="H40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K40" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="N40" t="s">
+        <v>169</v>
       </c>
       <c r="P40" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q40" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2990,13 +2984,13 @@
         <v>170</v>
       </c>
       <c r="P41" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q41" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -3016,13 +3010,13 @@
         <v>69</v>
       </c>
       <c r="F42">
-        <v>29.071</v>
+        <v>29.07028</v>
       </c>
       <c r="G42">
-        <v>-80.9263</v>
+        <v>-80.9258</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -3037,13 +3031,13 @@
         <v>171</v>
       </c>
       <c r="P42" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q42" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R42" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -3084,13 +3078,13 @@
         <v>172</v>
       </c>
       <c r="P43" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q43" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R43" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -3131,13 +3125,13 @@
         <v>173</v>
       </c>
       <c r="P44" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -3166,7 +3160,7 @@
         <v>7</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
         <v>101</v>
@@ -3174,17 +3168,14 @@
       <c r="K45" t="s">
         <v>131</v>
       </c>
-      <c r="N45" t="s">
-        <v>174</v>
-      </c>
       <c r="P45" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q45" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R45" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -3192,43 +3183,46 @@
         <v>45</v>
       </c>
       <c r="B46" s="1">
-        <v>43137</v>
+        <v>43136</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E46" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F46">
-        <v>29.07028</v>
+        <v>29.66549</v>
       </c>
       <c r="G46">
-        <v>-80.9258</v>
+        <v>-85.3488</v>
       </c>
       <c r="H46">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I46">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K46" t="s">
-        <v>131</v>
+        <v>128</v>
+      </c>
+      <c r="N46" t="s">
+        <v>174</v>
       </c>
       <c r="P46" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R46" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -3236,46 +3230,49 @@
         <v>46</v>
       </c>
       <c r="B47" s="1">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="C47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F47">
-        <v>29.66549</v>
+        <v>30.32741</v>
       </c>
       <c r="G47">
-        <v>-85.3488</v>
+        <v>-87.3137</v>
       </c>
       <c r="H47">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I47">
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K47" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N47" t="s">
         <v>175</v>
       </c>
+      <c r="O47" t="s">
+        <v>224</v>
+      </c>
       <c r="P47" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -3283,34 +3280,34 @@
         <v>47</v>
       </c>
       <c r="B48" s="1">
-        <v>43137</v>
+        <v>43144</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F48">
-        <v>30.32741</v>
+        <v>25.4792</v>
       </c>
       <c r="G48">
-        <v>-87.3137</v>
+        <v>-81.18680000000001</v>
       </c>
       <c r="H48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I48">
         <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K48" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N48" t="s">
         <v>176</v>
@@ -3319,13 +3316,13 @@
         <v>225</v>
       </c>
       <c r="P48" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q48" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -3354,7 +3351,7 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J49" t="s">
         <v>104</v>
@@ -3362,20 +3359,17 @@
       <c r="K49" t="s">
         <v>133</v>
       </c>
-      <c r="N49" t="s">
-        <v>177</v>
-      </c>
       <c r="O49" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P49" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q49" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -3395,16 +3389,16 @@
         <v>72</v>
       </c>
       <c r="F50">
-        <v>25.4792</v>
+        <v>25.50993</v>
       </c>
       <c r="G50">
-        <v>-81.18680000000001</v>
+        <v>-81.20950000000001</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J50" t="s">
         <v>104</v>
@@ -3413,16 +3407,16 @@
         <v>133</v>
       </c>
       <c r="O50" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -3430,46 +3424,46 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>43144</v>
+        <v>43139</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F51">
-        <v>25.50993</v>
+        <v>30.410008</v>
       </c>
       <c r="G51">
-        <v>-81.20950000000001</v>
+        <v>-81.40774399999999</v>
       </c>
       <c r="H51">
         <v>3</v>
       </c>
       <c r="I51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O51" t="s">
         <v>226</v>
       </c>
       <c r="P51" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q51" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -3477,46 +3471,43 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="C52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F52">
-        <v>30.410008</v>
+        <v>26.86351</v>
       </c>
       <c r="G52">
-        <v>-81.40774399999999</v>
+        <v>-80.0475</v>
       </c>
       <c r="H52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K52" t="s">
-        <v>134</v>
-      </c>
-      <c r="O52" t="s">
-        <v>227</v>
+        <v>135</v>
       </c>
       <c r="P52" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q52" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -3524,43 +3515,43 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>43137</v>
+        <v>43135</v>
       </c>
       <c r="C53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D53" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E53" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F53">
-        <v>26.86351</v>
+        <v>26.6232</v>
       </c>
       <c r="G53">
-        <v>-80.0475</v>
+        <v>-80.0406</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K53" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q53" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R53" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -3568,43 +3559,46 @@
         <v>53</v>
       </c>
       <c r="B54" s="1">
-        <v>43135</v>
+        <v>43137</v>
       </c>
       <c r="C54" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D54" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F54">
-        <v>26.6232</v>
+        <v>29.87753</v>
       </c>
       <c r="G54">
-        <v>-80.0406</v>
+        <v>-84.5711</v>
       </c>
       <c r="H54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I54">
         <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K54" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="N54" t="s">
+        <v>177</v>
       </c>
       <c r="P54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q54" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R54" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -3641,17 +3635,14 @@
       <c r="K55" t="s">
         <v>137</v>
       </c>
-      <c r="N55" t="s">
-        <v>178</v>
-      </c>
       <c r="P55" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q55" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R55" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -3671,13 +3662,13 @@
         <v>76</v>
       </c>
       <c r="F56">
-        <v>29.87753</v>
+        <v>29.87701</v>
       </c>
       <c r="G56">
-        <v>-84.5711</v>
+        <v>-84.5727</v>
       </c>
       <c r="H56">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I56">
         <v>1</v>
@@ -3688,14 +3679,17 @@
       <c r="K56" t="s">
         <v>137</v>
       </c>
+      <c r="N56" t="s">
+        <v>178</v>
+      </c>
       <c r="P56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q56" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R56" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -3736,13 +3730,13 @@
         <v>179</v>
       </c>
       <c r="P57" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q57" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R57" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -3783,13 +3777,13 @@
         <v>180</v>
       </c>
       <c r="P58" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -3818,7 +3812,7 @@
         <v>6</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="s">
         <v>108</v>
@@ -3826,17 +3820,14 @@
       <c r="K59" t="s">
         <v>137</v>
       </c>
-      <c r="N59" t="s">
-        <v>181</v>
-      </c>
       <c r="P59" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q59" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R59" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -3856,16 +3847,16 @@
         <v>76</v>
       </c>
       <c r="F60">
-        <v>29.87701</v>
+        <v>29.87547</v>
       </c>
       <c r="G60">
-        <v>-84.5727</v>
+        <v>-84.5741</v>
       </c>
       <c r="H60">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" t="s">
         <v>108</v>
@@ -3873,14 +3864,17 @@
       <c r="K60" t="s">
         <v>137</v>
       </c>
+      <c r="N60" t="s">
+        <v>181</v>
+      </c>
       <c r="P60" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q60" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R60" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -3909,7 +3903,7 @@
         <v>9</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="s">
         <v>108</v>
@@ -3917,17 +3911,14 @@
       <c r="K61" t="s">
         <v>137</v>
       </c>
-      <c r="N61" t="s">
-        <v>182</v>
-      </c>
       <c r="P61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R61" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -3947,13 +3938,13 @@
         <v>76</v>
       </c>
       <c r="F62">
-        <v>29.87547</v>
+        <v>29.8754</v>
       </c>
       <c r="G62">
-        <v>-84.5741</v>
+        <v>-84.57729999999999</v>
       </c>
       <c r="H62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I62">
         <v>2</v>
@@ -3965,13 +3956,13 @@
         <v>137</v>
       </c>
       <c r="P62" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q62" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R62" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -3991,16 +3982,16 @@
         <v>76</v>
       </c>
       <c r="F63">
-        <v>29.8754</v>
+        <v>29.87467</v>
       </c>
       <c r="G63">
-        <v>-84.57729999999999</v>
+        <v>-84.5787</v>
       </c>
       <c r="H63">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" t="s">
         <v>108</v>
@@ -4008,14 +3999,17 @@
       <c r="K63" t="s">
         <v>137</v>
       </c>
+      <c r="N63" t="s">
+        <v>182</v>
+      </c>
       <c r="P63" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q63" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R63" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -4056,13 +4050,13 @@
         <v>183</v>
       </c>
       <c r="P64" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q64" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R64" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -4091,7 +4085,7 @@
         <v>11</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J65" t="s">
         <v>108</v>
@@ -4099,17 +4093,14 @@
       <c r="K65" t="s">
         <v>137</v>
       </c>
-      <c r="N65" t="s">
-        <v>184</v>
-      </c>
       <c r="P65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q65" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R65" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -4120,40 +4111,46 @@
         <v>43137</v>
       </c>
       <c r="C66" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F66">
-        <v>29.87467</v>
+        <v>30.4847</v>
       </c>
       <c r="G66">
-        <v>-84.5787</v>
+        <v>-81.4153</v>
       </c>
       <c r="H66">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K66" t="s">
-        <v>137</v>
+        <v>127</v>
+      </c>
+      <c r="N66" t="s">
+        <v>184</v>
+      </c>
+      <c r="O66" t="s">
+        <v>227</v>
       </c>
       <c r="P66" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q66" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R66" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4194,16 +4191,16 @@
         <v>185</v>
       </c>
       <c r="O67" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P67" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q67" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R67" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -4244,16 +4241,16 @@
         <v>186</v>
       </c>
       <c r="O68" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P68" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q68" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R68" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -4294,16 +4291,16 @@
         <v>187</v>
       </c>
       <c r="O69" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P69" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q69" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R69" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -4344,16 +4341,16 @@
         <v>188</v>
       </c>
       <c r="O70" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P70" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q70" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R70" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -4394,16 +4391,16 @@
         <v>189</v>
       </c>
       <c r="O71" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P71" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q71" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R71" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4444,16 +4441,16 @@
         <v>190</v>
       </c>
       <c r="O72" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q72" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R72" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -4482,7 +4479,7 @@
         <v>4</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J73" t="s">
         <v>109</v>
@@ -4490,20 +4487,17 @@
       <c r="K73" t="s">
         <v>127</v>
       </c>
-      <c r="N73" t="s">
-        <v>191</v>
-      </c>
       <c r="O73" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P73" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q73" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R73" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -4523,16 +4517,16 @@
         <v>77</v>
       </c>
       <c r="F74">
-        <v>30.4847</v>
+        <v>30.43977</v>
       </c>
       <c r="G74">
-        <v>-81.4153</v>
+        <v>-81.4081</v>
       </c>
       <c r="H74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I74">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J74" t="s">
         <v>109</v>
@@ -4540,17 +4534,20 @@
       <c r="K74" t="s">
         <v>127</v>
       </c>
+      <c r="N74" t="s">
+        <v>191</v>
+      </c>
       <c r="O74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P74" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q74" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R74" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -4579,7 +4576,7 @@
         <v>5</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J75" t="s">
         <v>109</v>
@@ -4587,20 +4584,17 @@
       <c r="K75" t="s">
         <v>127</v>
       </c>
-      <c r="N75" t="s">
-        <v>192</v>
-      </c>
       <c r="O75" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P75" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q75" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R75" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -4620,16 +4614,16 @@
         <v>77</v>
       </c>
       <c r="F76">
-        <v>30.43977</v>
+        <v>30.4329</v>
       </c>
       <c r="G76">
-        <v>-81.4081</v>
+        <v>-81.407</v>
       </c>
       <c r="H76">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J76" t="s">
         <v>109</v>
@@ -4638,16 +4632,16 @@
         <v>127</v>
       </c>
       <c r="O76" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P76" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R76" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -4658,43 +4652,40 @@
         <v>43137</v>
       </c>
       <c r="C77" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D77" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E77" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F77">
-        <v>30.4329</v>
+        <v>24.80786</v>
       </c>
       <c r="G77">
-        <v>-81.407</v>
+        <v>-80.83499999999999</v>
       </c>
       <c r="H77">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I77">
         <v>1</v>
       </c>
       <c r="J77" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="K77" t="s">
-        <v>127</v>
-      </c>
-      <c r="O77" t="s">
-        <v>228</v>
+        <v>124</v>
       </c>
       <c r="P77" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q77" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R77" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -4714,16 +4705,16 @@
         <v>78</v>
       </c>
       <c r="F78">
-        <v>24.80786</v>
+        <v>24.80772</v>
       </c>
       <c r="G78">
-        <v>-80.83499999999999</v>
+        <v>-80.8355</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78" t="s">
         <v>94</v>
@@ -4732,13 +4723,13 @@
         <v>124</v>
       </c>
       <c r="P78" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R78" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -4749,40 +4740,43 @@
         <v>43137</v>
       </c>
       <c r="C79" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E79" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F79">
-        <v>24.80772</v>
+        <v>27.17168</v>
       </c>
       <c r="G79">
-        <v>-80.8355</v>
+        <v>-80.1833</v>
       </c>
       <c r="H79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J79" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="K79" t="s">
-        <v>124</v>
+        <v>136</v>
+      </c>
+      <c r="N79" t="s">
+        <v>192</v>
       </c>
       <c r="P79" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q79" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R79" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -4819,17 +4813,14 @@
       <c r="K80" t="s">
         <v>136</v>
       </c>
-      <c r="N80" t="s">
-        <v>193</v>
-      </c>
       <c r="P80" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q80" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R80" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -4837,22 +4828,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="1">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D81" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E81" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F81">
-        <v>27.17168</v>
+        <v>25.85589</v>
       </c>
       <c r="G81">
-        <v>-80.1833</v>
+        <v>-81.68340000000001</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -4861,19 +4852,22 @@
         <v>1</v>
       </c>
       <c r="J81" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K81" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="N81" t="s">
+        <v>193</v>
       </c>
       <c r="P81" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q81" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R81" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -4914,13 +4908,13 @@
         <v>194</v>
       </c>
       <c r="P82" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q82" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R82" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -4961,13 +4955,13 @@
         <v>195</v>
       </c>
       <c r="P83" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q83" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R83" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" spans="1:18">
@@ -5008,13 +5002,13 @@
         <v>196</v>
       </c>
       <c r="P84" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q84" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R84" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="85" spans="1:18">
@@ -5043,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J85" t="s">
         <v>111</v>
@@ -5051,17 +5045,14 @@
       <c r="K85" t="s">
         <v>138</v>
       </c>
-      <c r="N85" t="s">
-        <v>197</v>
-      </c>
       <c r="P85" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q85" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R85" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="86" spans="1:18">
@@ -5069,43 +5060,40 @@
         <v>85</v>
       </c>
       <c r="B86" s="1">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
-      </c>
-      <c r="D86" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E86" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F86">
-        <v>25.85589</v>
+        <v>27.43161</v>
       </c>
       <c r="G86">
-        <v>-81.68340000000001</v>
+        <v>-80.27630000000001</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J86" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K86" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P86" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q86" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R86" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="87" spans="1:18">
@@ -5122,16 +5110,16 @@
         <v>81</v>
       </c>
       <c r="F87">
-        <v>27.43161</v>
+        <v>27.43255</v>
       </c>
       <c r="G87">
-        <v>-80.27630000000001</v>
+        <v>-80.27670000000001</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" t="s">
         <v>112</v>
@@ -5139,14 +5127,17 @@
       <c r="K87" t="s">
         <v>139</v>
       </c>
+      <c r="N87" t="s">
+        <v>197</v>
+      </c>
       <c r="P87" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q87" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R87" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:18">
@@ -5154,43 +5145,46 @@
         <v>87</v>
       </c>
       <c r="B88" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="C88" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="D88" t="s">
+        <v>46</v>
       </c>
       <c r="E88" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F88">
-        <v>27.43255</v>
+        <v>30.3858</v>
       </c>
       <c r="G88">
-        <v>-80.27670000000001</v>
+        <v>-86.8536</v>
       </c>
       <c r="H88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I88">
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K88" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N88" t="s">
         <v>198</v>
       </c>
       <c r="P88" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q88" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R88" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -5198,46 +5192,49 @@
         <v>88</v>
       </c>
       <c r="B89" s="1">
-        <v>43137</v>
+        <v>43134</v>
       </c>
       <c r="C89" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D89" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E89" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F89">
-        <v>30.3858</v>
+        <v>27.6495</v>
       </c>
       <c r="G89">
-        <v>-86.8536</v>
+        <v>-82.7501</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89">
         <v>1</v>
       </c>
       <c r="J89" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K89" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N89" t="s">
         <v>199</v>
       </c>
+      <c r="O89" t="s">
+        <v>228</v>
+      </c>
       <c r="P89" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q89" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R89" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -5266,7 +5263,7 @@
         <v>2</v>
       </c>
       <c r="I90">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J90" t="s">
         <v>114</v>
@@ -5274,20 +5271,17 @@
       <c r="K90" t="s">
         <v>141</v>
       </c>
-      <c r="N90" t="s">
-        <v>200</v>
-      </c>
       <c r="O90" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P90" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q90" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R90" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -5298,43 +5292,46 @@
         <v>43134</v>
       </c>
       <c r="C91" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D91" t="s">
         <v>47</v>
       </c>
       <c r="E91" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F91">
-        <v>27.6495</v>
+        <v>27.6559</v>
       </c>
       <c r="G91">
-        <v>-82.7501</v>
+        <v>-82.7393</v>
       </c>
       <c r="H91">
         <v>2</v>
       </c>
       <c r="I91">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J91" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K91" t="s">
         <v>141</v>
       </c>
+      <c r="N91" t="s">
+        <v>200</v>
+      </c>
       <c r="O91" t="s">
         <v>229</v>
       </c>
       <c r="P91" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q91" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R91" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="1:18">
@@ -5371,20 +5368,17 @@
       <c r="K92" t="s">
         <v>141</v>
       </c>
-      <c r="N92" t="s">
-        <v>201</v>
-      </c>
       <c r="O92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P92" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q92" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R92" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -5404,13 +5398,13 @@
         <v>84</v>
       </c>
       <c r="F93">
-        <v>27.6559</v>
+        <v>27.6501</v>
       </c>
       <c r="G93">
-        <v>-82.7393</v>
+        <v>-82.7347</v>
       </c>
       <c r="H93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -5421,17 +5415,20 @@
       <c r="K93" t="s">
         <v>141</v>
       </c>
+      <c r="N93" t="s">
+        <v>201</v>
+      </c>
       <c r="O93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P93" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q93" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R93" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -5460,7 +5457,7 @@
         <v>3</v>
       </c>
       <c r="I94">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J94" t="s">
         <v>115</v>
@@ -5468,20 +5465,17 @@
       <c r="K94" t="s">
         <v>141</v>
       </c>
-      <c r="N94" t="s">
-        <v>202</v>
-      </c>
       <c r="O94" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P94" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q94" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R94" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" spans="1:18">
@@ -5489,7 +5483,7 @@
         <v>94</v>
       </c>
       <c r="B95" s="1">
-        <v>43134</v>
+        <v>43138</v>
       </c>
       <c r="C95" t="s">
         <v>38</v>
@@ -5498,37 +5492,37 @@
         <v>47</v>
       </c>
       <c r="E95" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F95">
-        <v>27.6501</v>
+        <v>29.63802</v>
       </c>
       <c r="G95">
-        <v>-82.7347</v>
+        <v>-85.148</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I95">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J95" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K95" t="s">
-        <v>141</v>
-      </c>
-      <c r="O95" t="s">
-        <v>230</v>
+        <v>142</v>
+      </c>
+      <c r="N95" t="s">
+        <v>202</v>
       </c>
       <c r="P95" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R95" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" spans="1:18">
@@ -5565,17 +5559,14 @@
       <c r="K96" t="s">
         <v>142</v>
       </c>
-      <c r="N96" t="s">
-        <v>203</v>
-      </c>
       <c r="P96" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q96" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R96" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" spans="1:18">
@@ -5586,40 +5577,43 @@
         <v>43138</v>
       </c>
       <c r="C97" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D97" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E97" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F97">
-        <v>29.63802</v>
+        <v>29.71343</v>
       </c>
       <c r="G97">
-        <v>-85.148</v>
+        <v>-84.7499</v>
       </c>
       <c r="H97">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I97">
         <v>1</v>
       </c>
       <c r="J97" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K97" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="N97" t="s">
+        <v>203</v>
       </c>
       <c r="P97" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q97" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R97" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -5639,13 +5633,13 @@
         <v>86</v>
       </c>
       <c r="F98">
-        <v>29.71343</v>
+        <v>29.71624</v>
       </c>
       <c r="G98">
-        <v>-84.7499</v>
+        <v>-84.7466</v>
       </c>
       <c r="H98">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -5656,17 +5650,14 @@
       <c r="K98" t="s">
         <v>143</v>
       </c>
-      <c r="N98" t="s">
-        <v>204</v>
-      </c>
       <c r="P98" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q98" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R98" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -5686,13 +5677,13 @@
         <v>86</v>
       </c>
       <c r="F99">
-        <v>29.71624</v>
+        <v>29.71831</v>
       </c>
       <c r="G99">
-        <v>-84.7466</v>
+        <v>-84.744</v>
       </c>
       <c r="H99">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I99">
         <v>1</v>
@@ -5703,14 +5694,17 @@
       <c r="K99" t="s">
         <v>143</v>
       </c>
+      <c r="N99" t="s">
+        <v>204</v>
+      </c>
       <c r="P99" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q99" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R99" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -5730,13 +5724,13 @@
         <v>86</v>
       </c>
       <c r="F100">
-        <v>29.71831</v>
+        <v>29.73627</v>
       </c>
       <c r="G100">
-        <v>-84.744</v>
+        <v>-84.7229</v>
       </c>
       <c r="H100">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -5751,13 +5745,13 @@
         <v>205</v>
       </c>
       <c r="P100" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q100" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R100" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:18">
@@ -5777,13 +5771,13 @@
         <v>86</v>
       </c>
       <c r="F101">
-        <v>29.73627</v>
+        <v>29.7464</v>
       </c>
       <c r="G101">
-        <v>-84.7229</v>
+        <v>-84.7123</v>
       </c>
       <c r="H101">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I101">
         <v>1</v>
@@ -5798,13 +5792,13 @@
         <v>206</v>
       </c>
       <c r="P101" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q101" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R101" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -5845,13 +5839,13 @@
         <v>207</v>
       </c>
       <c r="P102" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q102" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R102" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -5888,17 +5882,14 @@
       <c r="K103" t="s">
         <v>143</v>
       </c>
-      <c r="N103" t="s">
-        <v>208</v>
-      </c>
       <c r="P103" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q103" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R103" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:18">
@@ -5906,43 +5897,43 @@
         <v>103</v>
       </c>
       <c r="B104" s="1">
-        <v>43138</v>
+        <v>43133</v>
       </c>
       <c r="C104" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D104" t="s">
         <v>51</v>
       </c>
       <c r="E104" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F104">
-        <v>29.7464</v>
+        <v>28.13208</v>
       </c>
       <c r="G104">
-        <v>-84.7123</v>
+        <v>-82.8282</v>
       </c>
       <c r="H104">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I104">
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K104" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P104" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q104" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R104" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -5953,40 +5944,43 @@
         <v>43133</v>
       </c>
       <c r="C105" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D105" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E105" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F105">
-        <v>28.13208</v>
+        <v>28.11171</v>
       </c>
       <c r="G105">
-        <v>-82.8282</v>
+        <v>-82.837</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I105">
         <v>1</v>
       </c>
       <c r="J105" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K105" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="N105" t="s">
+        <v>208</v>
       </c>
       <c r="P105" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q105" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R105" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6027,13 +6021,13 @@
         <v>209</v>
       </c>
       <c r="P106" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q106" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R106" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6074,13 +6068,13 @@
         <v>210</v>
       </c>
       <c r="P107" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q107" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R107" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -6121,13 +6115,13 @@
         <v>211</v>
       </c>
       <c r="P108" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q108" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R108" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -6168,13 +6162,13 @@
         <v>212</v>
       </c>
       <c r="P109" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q109" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R109" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -6215,13 +6209,13 @@
         <v>213</v>
       </c>
       <c r="P110" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q110" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R110" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -6262,13 +6256,13 @@
         <v>214</v>
       </c>
       <c r="P111" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q111" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R111" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -6297,7 +6291,7 @@
         <v>2</v>
       </c>
       <c r="I112">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J112" t="s">
         <v>119</v>
@@ -6305,17 +6299,14 @@
       <c r="K112" t="s">
         <v>145</v>
       </c>
-      <c r="N112" t="s">
-        <v>215</v>
-      </c>
       <c r="P112" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q112" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R112" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -6326,40 +6317,46 @@
         <v>43133</v>
       </c>
       <c r="C113" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D113" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E113" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F113">
-        <v>28.11171</v>
+        <v>30.06609</v>
       </c>
       <c r="G113">
-        <v>-82.837</v>
+        <v>-85.6161</v>
       </c>
       <c r="H113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I113">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J113" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="K113" t="s">
-        <v>145</v>
+        <v>121</v>
+      </c>
+      <c r="N113" t="s">
+        <v>215</v>
+      </c>
+      <c r="O113" t="s">
+        <v>230</v>
       </c>
       <c r="P113" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q113" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R113" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -6400,16 +6397,16 @@
         <v>216</v>
       </c>
       <c r="O114" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P114" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q114" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R114" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" spans="1:18">
@@ -6450,16 +6447,16 @@
         <v>217</v>
       </c>
       <c r="O115" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P115" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q115" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R115" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:18">
@@ -6500,16 +6497,16 @@
         <v>218</v>
       </c>
       <c r="O116" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P116" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q116" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R116" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -6546,20 +6543,17 @@
       <c r="K117" t="s">
         <v>121</v>
       </c>
-      <c r="N117" t="s">
-        <v>219</v>
-      </c>
       <c r="O117" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P117" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q117" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R117" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -6579,13 +6573,13 @@
         <v>89</v>
       </c>
       <c r="F118">
-        <v>30.06609</v>
+        <v>30.08727</v>
       </c>
       <c r="G118">
-        <v>-85.6161</v>
+        <v>-85.6602</v>
       </c>
       <c r="H118">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I118">
         <v>1</v>
@@ -6596,17 +6590,20 @@
       <c r="K118" t="s">
         <v>121</v>
       </c>
+      <c r="N118" t="s">
+        <v>219</v>
+      </c>
       <c r="O118" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P118" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q118" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R118" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -6647,16 +6644,16 @@
         <v>220</v>
       </c>
       <c r="O119" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P119" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q119" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R119" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:18">
@@ -6664,96 +6661,46 @@
         <v>119</v>
       </c>
       <c r="B120" s="1">
-        <v>43133</v>
+        <v>43137</v>
       </c>
       <c r="C120" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D120" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E120" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F120">
-        <v>30.08727</v>
+        <v>29.30722</v>
       </c>
       <c r="G120">
-        <v>-85.6602</v>
+        <v>-81.0467</v>
       </c>
       <c r="H120">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="K120" t="s">
-        <v>121</v>
-      </c>
-      <c r="N120" t="s">
-        <v>221</v>
+        <v>146</v>
       </c>
       <c r="O120" t="s">
         <v>231</v>
       </c>
       <c r="P120" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q120" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R120" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18">
-      <c r="A121">
-        <v>120</v>
-      </c>
-      <c r="B121" s="1">
-        <v>43137</v>
-      </c>
-      <c r="C121" t="s">
-        <v>43</v>
-      </c>
-      <c r="D121" t="s">
-        <v>47</v>
-      </c>
-      <c r="E121" t="s">
-        <v>90</v>
-      </c>
-      <c r="F121">
-        <v>29.30722</v>
-      </c>
-      <c r="G121">
-        <v>-81.0467</v>
-      </c>
-      <c r="H121">
-        <v>6</v>
-      </c>
-      <c r="I121">
-        <v>2</v>
-      </c>
-      <c r="J121" t="s">
-        <v>120</v>
-      </c>
-      <c r="K121" t="s">
-        <v>146</v>
-      </c>
-      <c r="O121" t="s">
-        <v>232</v>
-      </c>
-      <c r="P121" t="s">
-        <v>233</v>
-      </c>
-      <c r="Q121" t="s">
-        <v>234</v>
-      </c>
-      <c r="R121" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Databases/Database3/Output/2018/db3_2018_clean.xlsx
+++ b/Databases/Database3/Output/2018/db3_2018_clean.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1088" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="233">
   <si>
     <t>unique_id</t>
   </si>
@@ -502,49 +502,46 @@
     <t>Yf(9C8)//WB:S//bO</t>
   </si>
   <si>
-    <t>X:X (not banded) 6 total for this point</t>
-  </si>
-  <si>
     <t>LL=FO,G/K RL=_,B</t>
   </si>
   <si>
-    <t>bf (missing) S, Y/G: -, G/K (photo; 5th winter)</t>
-  </si>
-  <si>
-    <t>Gf (5TH), -: O, - (photo; 3rd winter)</t>
-  </si>
-  <si>
-    <t>O (green dot), O/Y: S, - (photo; 3rd winter)</t>
-  </si>
-  <si>
-    <t>Gf (M9E), -: O, - (photo)</t>
-  </si>
-  <si>
-    <t>Yf (4Y?), -: S, - (photo)</t>
-  </si>
-  <si>
-    <t>PPI: (UL) FO, (LL) K/O/Y, (UR) S, (LR) Lb (reported to bander);</t>
-  </si>
-  <si>
-    <t>(UL) S, (LL) Y, (UR) -, (LR) O (reported to bander)</t>
-  </si>
-  <si>
-    <t>Band/Flag Code: HY: (UL) S, (LL) -, (UR) FK, (LR) -(reported);</t>
-  </si>
-  <si>
-    <t>(UL) S, (LL) B, (UR) FO, (LR) R/Y (reported);</t>
-  </si>
-  <si>
-    <t>Band/flag code: LMX: (UL) FG, (LL) -, (UR) B, (LR) - (reported)</t>
+    <t>bf (missing) S, Y/G: -, G/K</t>
+  </si>
+  <si>
+    <t>Gf (5TH), -: O, -</t>
+  </si>
+  <si>
+    <t>O (green dot), O/Y: S, -</t>
+  </si>
+  <si>
+    <t>Gf (M9E), -: O, -</t>
+  </si>
+  <si>
+    <t>Yf (4Y?), -: S, -</t>
+  </si>
+  <si>
+    <t>(UL) FO, (LL) K/O/Y, (UR) S, (LR) Lb</t>
+  </si>
+  <si>
+    <t>(UL) S, (LL) Y, (UR) -, (LR) O</t>
+  </si>
+  <si>
+    <t>(UL) S, (LL) -, (UR) FK, (LR) ;</t>
+  </si>
+  <si>
+    <t>(UL) S, (LL) B, (UR) FO, (LR) R/Y;</t>
+  </si>
+  <si>
+    <t>LMX: (UL) FG, (LL) -, (UR) B, (LR)</t>
   </si>
   <si>
     <t>S//:Bf(A97)//</t>
   </si>
   <si>
-    <t>S/LY:bf/LG (bf = light blue flag, no code); reported directly to bander</t>
-  </si>
-  <si>
-    <t>YX6, color: green, position: upper left". The "O" is for an orange band on the right leg, position: upper right.</t>
+    <t>S/LY:bf/LG</t>
+  </si>
+  <si>
+    <t>fg(YX6)/-:O/M</t>
   </si>
   <si>
     <t>S//BK:Bf(C63)//YB</t>
@@ -556,7 +553,7 @@
     <t>Yf(J87)//RO:S//YB</t>
   </si>
   <si>
-    <t>S//RY:Yf(E60)//YK- all reported to the banders</t>
+    <t>S//RY:Yf(E60)//YK</t>
   </si>
   <si>
     <t>Yf(6H1)//:S//</t>
@@ -589,37 +586,37 @@
     <t>FW[VA],_:S,_</t>
   </si>
   <si>
-    <t>Banded - FK[UN], _ : S, _</t>
-  </si>
-  <si>
-    <t>Left leg: Orange flag, upper yellow band, lower green band. Right leg: Upper silver USFWS band, lower Yellow band</t>
-  </si>
-  <si>
-    <t>fY(20E),BO:X,Rb continuing bird, will be batch reported at end of season.</t>
-  </si>
-  <si>
-    <t>G,-:fG(K5K),- continuing bird, will be batch reported at end of season.</t>
-  </si>
-  <si>
-    <t>X,-:fK(KT),- continuing bird, will be batch reported at end of season.</t>
-  </si>
-  <si>
-    <t>X,O/R:O(B.),R(125) reported to Great Lakes Plover coordinators</t>
-  </si>
-  <si>
-    <t>left-- green flag NLP, right-- blue band</t>
-  </si>
-  <si>
-    <t>Silver band//white : yellow flag//black</t>
-  </si>
-  <si>
-    <t>-, O : S, Y-O split band Reported to Great Lakes researchers</t>
-  </si>
-  <si>
-    <t>S, B-O split : O, B Reported to Great Lakes researcher</t>
-  </si>
-  <si>
-    <t>S, K : FO, B/Y FTP; Y; FTP, - : -, - reported to Great Lakes area researchers</t>
+    <t>FK[UN], _ : S, _</t>
+  </si>
+  <si>
+    <t>FO/OG:M/-</t>
+  </si>
+  <si>
+    <t>fY(20E),BO:X,Rb</t>
+  </si>
+  <si>
+    <t>G,-:fG(K5K)</t>
+  </si>
+  <si>
+    <t>X,-:fK(KT)</t>
+  </si>
+  <si>
+    <t>X,O/R:O(B.),R(125)</t>
+  </si>
+  <si>
+    <t>FG(NLP)/-:B/M</t>
+  </si>
+  <si>
+    <t>M/W:FY/N</t>
+  </si>
+  <si>
+    <t>-, O : S, Y-O</t>
+  </si>
+  <si>
+    <t>M/BO:O/B</t>
+  </si>
+  <si>
+    <t>S, K : FO, B/Y FTP</t>
   </si>
   <si>
     <t>S//x:YF(622)//x</t>
@@ -667,10 +664,10 @@
     <t>O(blue dot)//Y:S//Y/O</t>
   </si>
   <si>
-    <t>O//b:S//(missing band light blue, LR )</t>
-  </si>
-  <si>
-    <t>S//KY:Yf(H67)//W (missing band Red, LR)</t>
+    <t>O//b:S//</t>
+  </si>
+  <si>
+    <t>S//KY:Yf(H67)//W</t>
   </si>
   <si>
     <t>X//OG:Gf//KY</t>
@@ -692,9 +689,6 @@
   </si>
   <si>
     <t>End time was 13:45</t>
-  </si>
-  <si>
-    <t>GPS borrowed from 2024 — point 3 had no coordinates in 2018</t>
   </si>
   <si>
     <t>Sunny, fair weather, rising tide, low at 6:55 a.m.</t>
@@ -1054,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R120"/>
+  <dimension ref="A1:R119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1148,16 +1142,16 @@
         <v>121</v>
       </c>
       <c r="O2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1195,16 +1189,16 @@
         <v>121</v>
       </c>
       <c r="O3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1245,16 +1239,16 @@
         <v>147</v>
       </c>
       <c r="O4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1295,16 +1289,16 @@
         <v>148</v>
       </c>
       <c r="O5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1345,16 +1339,16 @@
         <v>149</v>
       </c>
       <c r="O6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1395,16 +1389,16 @@
         <v>150</v>
       </c>
       <c r="O7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -1445,16 +1439,16 @@
         <v>151</v>
       </c>
       <c r="O8" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P8" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q8" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R8" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1495,16 +1489,16 @@
         <v>152</v>
       </c>
       <c r="O9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1545,16 +1539,16 @@
         <v>153</v>
       </c>
       <c r="O10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1595,16 +1589,16 @@
         <v>154</v>
       </c>
       <c r="O11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1645,16 +1639,16 @@
         <v>155</v>
       </c>
       <c r="O12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P12" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1695,16 +1689,16 @@
         <v>156</v>
       </c>
       <c r="O13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1745,16 +1739,16 @@
         <v>157</v>
       </c>
       <c r="O14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q14" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1792,16 +1786,16 @@
         <v>121</v>
       </c>
       <c r="O15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P15" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R15" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1842,13 +1836,13 @@
         <v>158</v>
       </c>
       <c r="P16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1889,13 +1883,13 @@
         <v>159</v>
       </c>
       <c r="P17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -1933,13 +1927,13 @@
         <v>122</v>
       </c>
       <c r="P18" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q18" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:18">
@@ -1977,13 +1971,13 @@
         <v>123</v>
       </c>
       <c r="P19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" spans="1:18">
@@ -2021,13 +2015,13 @@
         <v>123</v>
       </c>
       <c r="P20" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R20" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" spans="1:18">
@@ -2065,13 +2059,13 @@
         <v>123</v>
       </c>
       <c r="P21" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q21" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:18">
@@ -2109,13 +2103,13 @@
         <v>123</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q22" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R22" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="23" spans="1:18">
@@ -2153,13 +2147,13 @@
         <v>124</v>
       </c>
       <c r="P23" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q23" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:18">
@@ -2197,13 +2191,13 @@
         <v>125</v>
       </c>
       <c r="P24" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R24" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:18">
@@ -2241,16 +2235,16 @@
         <v>126</v>
       </c>
       <c r="O25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:18">
@@ -2288,16 +2282,16 @@
         <v>127</v>
       </c>
       <c r="O26" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P26" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q26" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R26" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="27" spans="1:18">
@@ -2338,13 +2332,13 @@
         <v>160</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q27" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R27" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="28" spans="1:18">
@@ -2385,13 +2379,13 @@
         <v>161</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q28" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R28" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:18">
@@ -2420,7 +2414,7 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J29" t="s">
         <v>98</v>
@@ -2428,17 +2422,14 @@
       <c r="K29" t="s">
         <v>128</v>
       </c>
-      <c r="N29" t="s">
-        <v>162</v>
-      </c>
       <c r="P29" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q29" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R29" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="30" spans="1:18">
@@ -2449,40 +2440,43 @@
         <v>43133</v>
       </c>
       <c r="C30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F30">
-        <v>29.99092</v>
+        <v>28.05099</v>
       </c>
       <c r="G30">
-        <v>-85.502</v>
+        <v>-82.8197</v>
       </c>
       <c r="H30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K30" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="N30" t="s">
+        <v>162</v>
       </c>
       <c r="P30" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q30" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R30" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="31" spans="1:18">
@@ -2511,7 +2505,7 @@
         <v>2</v>
       </c>
       <c r="I31">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J31" t="s">
         <v>99</v>
@@ -2519,17 +2513,14 @@
       <c r="K31" t="s">
         <v>129</v>
       </c>
-      <c r="N31" t="s">
-        <v>163</v>
-      </c>
       <c r="P31" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q31" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R31" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="32" spans="1:18">
@@ -2537,43 +2528,46 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>43133</v>
+        <v>43134</v>
       </c>
       <c r="C32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F32">
-        <v>28.05099</v>
+        <v>25.70076</v>
       </c>
       <c r="G32">
-        <v>-82.8197</v>
+        <v>-80.1549</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K32" t="s">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="N32" t="s">
+        <v>163</v>
       </c>
       <c r="P32" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q32" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R32" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:18">
@@ -2614,13 +2608,13 @@
         <v>164</v>
       </c>
       <c r="P33" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q33" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R33" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:18">
@@ -2661,13 +2655,13 @@
         <v>165</v>
       </c>
       <c r="P34" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q34" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R34" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:18">
@@ -2708,13 +2702,13 @@
         <v>166</v>
       </c>
       <c r="P35" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:18">
@@ -2755,13 +2749,13 @@
         <v>167</v>
       </c>
       <c r="P36" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37" spans="1:18">
@@ -2790,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J37" t="s">
         <v>100</v>
@@ -2798,17 +2792,14 @@
       <c r="K37" t="s">
         <v>130</v>
       </c>
-      <c r="N37" t="s">
-        <v>168</v>
-      </c>
       <c r="P37" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q37" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R37" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="38" spans="1:18">
@@ -2828,16 +2819,16 @@
         <v>68</v>
       </c>
       <c r="F38">
-        <v>25.70076</v>
+        <v>25.70171</v>
       </c>
       <c r="G38">
-        <v>-80.1549</v>
+        <v>-80.1544</v>
       </c>
       <c r="H38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J38" t="s">
         <v>100</v>
@@ -2846,13 +2837,13 @@
         <v>130</v>
       </c>
       <c r="P38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q38" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="39" spans="1:18">
@@ -2860,43 +2851,46 @@
         <v>38</v>
       </c>
       <c r="B39" s="1">
-        <v>43134</v>
+        <v>43137</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F39">
-        <v>25.70171</v>
+        <v>29.071</v>
       </c>
       <c r="G39">
-        <v>-80.1544</v>
+        <v>-80.9263</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K39" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="N39" t="s">
+        <v>168</v>
       </c>
       <c r="P39" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q39" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R39" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="40" spans="1:18">
@@ -2937,13 +2931,13 @@
         <v>169</v>
       </c>
       <c r="P40" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q40" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:18">
@@ -2963,13 +2957,13 @@
         <v>69</v>
       </c>
       <c r="F41">
-        <v>29.071</v>
+        <v>29.07028</v>
       </c>
       <c r="G41">
-        <v>-80.9263</v>
+        <v>-80.9258</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -2984,13 +2978,13 @@
         <v>170</v>
       </c>
       <c r="P41" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q41" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R41" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="42" spans="1:18">
@@ -3031,13 +3025,13 @@
         <v>171</v>
       </c>
       <c r="P42" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:18">
@@ -3078,13 +3072,13 @@
         <v>172</v>
       </c>
       <c r="P43" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q43" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R43" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:18">
@@ -3113,7 +3107,7 @@
         <v>7</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
         <v>101</v>
@@ -3121,17 +3115,14 @@
       <c r="K44" t="s">
         <v>131</v>
       </c>
-      <c r="N44" t="s">
-        <v>173</v>
-      </c>
       <c r="P44" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q44" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:18">
@@ -3139,43 +3130,46 @@
         <v>44</v>
       </c>
       <c r="B45" s="1">
-        <v>43137</v>
+        <v>43136</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F45">
-        <v>29.07028</v>
+        <v>29.66549</v>
       </c>
       <c r="G45">
-        <v>-80.9258</v>
+        <v>-85.3488</v>
       </c>
       <c r="H45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I45">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K45" t="s">
-        <v>131</v>
+        <v>128</v>
+      </c>
+      <c r="N45" t="s">
+        <v>173</v>
       </c>
       <c r="P45" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q45" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R45" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:18">
@@ -3183,46 +3177,49 @@
         <v>45</v>
       </c>
       <c r="B46" s="1">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F46">
-        <v>29.66549</v>
+        <v>30.32741</v>
       </c>
       <c r="G46">
-        <v>-85.3488</v>
+        <v>-87.3137</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I46">
         <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K46" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N46" t="s">
         <v>174</v>
       </c>
+      <c r="O46" t="s">
+        <v>223</v>
+      </c>
       <c r="P46" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q46" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R46" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:18">
@@ -3230,34 +3227,34 @@
         <v>46</v>
       </c>
       <c r="B47" s="1">
-        <v>43137</v>
+        <v>43144</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F47">
-        <v>30.32741</v>
+        <v>25.4792</v>
       </c>
       <c r="G47">
-        <v>-87.3137</v>
+        <v>-81.18680000000001</v>
       </c>
       <c r="H47">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I47">
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K47" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N47" t="s">
         <v>175</v>
@@ -3266,13 +3263,13 @@
         <v>224</v>
       </c>
       <c r="P47" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q47" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R47" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="48" spans="1:18">
@@ -3301,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J48" t="s">
         <v>104</v>
@@ -3309,20 +3306,17 @@
       <c r="K48" t="s">
         <v>133</v>
       </c>
-      <c r="N48" t="s">
-        <v>176</v>
-      </c>
       <c r="O48" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P48" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q48" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R48" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:18">
@@ -3342,16 +3336,16 @@
         <v>72</v>
       </c>
       <c r="F49">
-        <v>25.4792</v>
+        <v>25.50993</v>
       </c>
       <c r="G49">
-        <v>-81.18680000000001</v>
+        <v>-81.20950000000001</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J49" t="s">
         <v>104</v>
@@ -3360,16 +3354,16 @@
         <v>133</v>
       </c>
       <c r="O49" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="P49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R49" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:18">
@@ -3377,46 +3371,43 @@
         <v>49</v>
       </c>
       <c r="B50" s="1">
-        <v>43144</v>
+        <v>43139</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F50">
-        <v>25.50993</v>
+        <v>30.410008</v>
       </c>
       <c r="G50">
-        <v>-81.20950000000001</v>
+        <v>-81.40774399999999</v>
       </c>
       <c r="H50">
         <v>3</v>
       </c>
       <c r="I50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K50" t="s">
-        <v>133</v>
-      </c>
-      <c r="O50" t="s">
-        <v>225</v>
+        <v>134</v>
       </c>
       <c r="P50" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q50" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R50" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:18">
@@ -3424,46 +3415,43 @@
         <v>50</v>
       </c>
       <c r="B51" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="C51" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F51">
-        <v>30.410008</v>
+        <v>26.86351</v>
       </c>
       <c r="G51">
-        <v>-81.40774399999999</v>
+        <v>-80.0475</v>
       </c>
       <c r="H51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K51" t="s">
-        <v>134</v>
-      </c>
-      <c r="O51" t="s">
-        <v>226</v>
+        <v>135</v>
       </c>
       <c r="P51" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q51" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:18">
@@ -3471,43 +3459,43 @@
         <v>51</v>
       </c>
       <c r="B52" s="1">
-        <v>43137</v>
+        <v>43135</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E52" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F52">
-        <v>26.86351</v>
+        <v>26.6232</v>
       </c>
       <c r="G52">
-        <v>-80.0475</v>
+        <v>-80.0406</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I52">
         <v>1</v>
       </c>
       <c r="J52" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P52" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q52" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R52" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="53" spans="1:18">
@@ -3515,43 +3503,46 @@
         <v>52</v>
       </c>
       <c r="B53" s="1">
-        <v>43135</v>
+        <v>43137</v>
       </c>
       <c r="C53" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D53" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F53">
-        <v>26.6232</v>
+        <v>29.87753</v>
       </c>
       <c r="G53">
-        <v>-80.0406</v>
+        <v>-84.5711</v>
       </c>
       <c r="H53">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I53">
         <v>1</v>
       </c>
       <c r="J53" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K53" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="N53" t="s">
+        <v>176</v>
       </c>
       <c r="P53" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q53" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:18">
@@ -3588,17 +3579,14 @@
       <c r="K54" t="s">
         <v>137</v>
       </c>
-      <c r="N54" t="s">
-        <v>177</v>
-      </c>
       <c r="P54" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q54" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R54" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:18">
@@ -3618,13 +3606,13 @@
         <v>76</v>
       </c>
       <c r="F55">
-        <v>29.87753</v>
+        <v>29.87701</v>
       </c>
       <c r="G55">
-        <v>-84.5711</v>
+        <v>-84.5727</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I55">
         <v>1</v>
@@ -3635,14 +3623,17 @@
       <c r="K55" t="s">
         <v>137</v>
       </c>
+      <c r="N55" t="s">
+        <v>177</v>
+      </c>
       <c r="P55" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q55" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R55" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="56" spans="1:18">
@@ -3683,13 +3674,13 @@
         <v>178</v>
       </c>
       <c r="P56" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q56" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R56" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="57" spans="1:18">
@@ -3730,13 +3721,13 @@
         <v>179</v>
       </c>
       <c r="P57" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q57" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R57" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="58" spans="1:18">
@@ -3765,7 +3756,7 @@
         <v>6</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J58" t="s">
         <v>108</v>
@@ -3773,17 +3764,14 @@
       <c r="K58" t="s">
         <v>137</v>
       </c>
-      <c r="N58" t="s">
-        <v>180</v>
-      </c>
       <c r="P58" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q58" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R58" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:18">
@@ -3803,16 +3791,16 @@
         <v>76</v>
       </c>
       <c r="F59">
-        <v>29.87701</v>
+        <v>29.87547</v>
       </c>
       <c r="G59">
-        <v>-84.5727</v>
+        <v>-84.5741</v>
       </c>
       <c r="H59">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" t="s">
         <v>108</v>
@@ -3820,14 +3808,17 @@
       <c r="K59" t="s">
         <v>137</v>
       </c>
+      <c r="N59" t="s">
+        <v>180</v>
+      </c>
       <c r="P59" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q59" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R59" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="60" spans="1:18">
@@ -3856,7 +3847,7 @@
         <v>9</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J60" t="s">
         <v>108</v>
@@ -3864,17 +3855,14 @@
       <c r="K60" t="s">
         <v>137</v>
       </c>
-      <c r="N60" t="s">
-        <v>181</v>
-      </c>
       <c r="P60" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q60" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R60" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="61" spans="1:18">
@@ -3894,13 +3882,13 @@
         <v>76</v>
       </c>
       <c r="F61">
-        <v>29.87547</v>
+        <v>29.8754</v>
       </c>
       <c r="G61">
-        <v>-84.5741</v>
+        <v>-84.57729999999999</v>
       </c>
       <c r="H61">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I61">
         <v>2</v>
@@ -3912,13 +3900,13 @@
         <v>137</v>
       </c>
       <c r="P61" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q61" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R61" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="62" spans="1:18">
@@ -3938,16 +3926,16 @@
         <v>76</v>
       </c>
       <c r="F62">
-        <v>29.8754</v>
+        <v>29.87467</v>
       </c>
       <c r="G62">
-        <v>-84.57729999999999</v>
+        <v>-84.5787</v>
       </c>
       <c r="H62">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J62" t="s">
         <v>108</v>
@@ -3955,14 +3943,17 @@
       <c r="K62" t="s">
         <v>137</v>
       </c>
+      <c r="N62" t="s">
+        <v>181</v>
+      </c>
       <c r="P62" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q62" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R62" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="63" spans="1:18">
@@ -4003,13 +3994,13 @@
         <v>182</v>
       </c>
       <c r="P63" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q63" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R63" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:18">
@@ -4038,7 +4029,7 @@
         <v>11</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J64" t="s">
         <v>108</v>
@@ -4046,17 +4037,14 @@
       <c r="K64" t="s">
         <v>137</v>
       </c>
-      <c r="N64" t="s">
-        <v>183</v>
-      </c>
       <c r="P64" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q64" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R64" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:18">
@@ -4067,40 +4055,46 @@
         <v>43137</v>
       </c>
       <c r="C65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F65">
-        <v>29.87467</v>
+        <v>30.4847</v>
       </c>
       <c r="G65">
-        <v>-84.5787</v>
+        <v>-81.4153</v>
       </c>
       <c r="H65">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J65" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K65" t="s">
-        <v>137</v>
+        <v>127</v>
+      </c>
+      <c r="N65" t="s">
+        <v>183</v>
+      </c>
+      <c r="O65" t="s">
+        <v>225</v>
       </c>
       <c r="P65" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q65" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R65" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:18">
@@ -4141,16 +4135,16 @@
         <v>184</v>
       </c>
       <c r="O66" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P66" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q66" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R66" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" spans="1:18">
@@ -4191,16 +4185,16 @@
         <v>185</v>
       </c>
       <c r="O67" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P67" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q67" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R67" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:18">
@@ -4241,16 +4235,16 @@
         <v>186</v>
       </c>
       <c r="O68" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P68" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q68" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R68" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:18">
@@ -4291,16 +4285,16 @@
         <v>187</v>
       </c>
       <c r="O69" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P69" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q69" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R69" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:18">
@@ -4341,16 +4335,16 @@
         <v>188</v>
       </c>
       <c r="O70" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P70" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q70" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R70" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:18">
@@ -4391,16 +4385,16 @@
         <v>189</v>
       </c>
       <c r="O71" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P71" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q71" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R71" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="72" spans="1:18">
@@ -4429,7 +4423,7 @@
         <v>4</v>
       </c>
       <c r="I72">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J72" t="s">
         <v>109</v>
@@ -4437,20 +4431,17 @@
       <c r="K72" t="s">
         <v>127</v>
       </c>
-      <c r="N72" t="s">
-        <v>190</v>
-      </c>
       <c r="O72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P72" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="73" spans="1:18">
@@ -4470,16 +4461,16 @@
         <v>77</v>
       </c>
       <c r="F73">
-        <v>30.4847</v>
+        <v>30.43977</v>
       </c>
       <c r="G73">
-        <v>-81.4153</v>
+        <v>-81.4081</v>
       </c>
       <c r="H73">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I73">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J73" t="s">
         <v>109</v>
@@ -4487,17 +4478,20 @@
       <c r="K73" t="s">
         <v>127</v>
       </c>
+      <c r="N73" t="s">
+        <v>190</v>
+      </c>
       <c r="O73" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P73" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q73" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R73" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:18">
@@ -4526,7 +4520,7 @@
         <v>5</v>
       </c>
       <c r="I74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J74" t="s">
         <v>109</v>
@@ -4534,20 +4528,17 @@
       <c r="K74" t="s">
         <v>127</v>
       </c>
-      <c r="N74" t="s">
-        <v>191</v>
-      </c>
       <c r="O74" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P74" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q74" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R74" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="75" spans="1:18">
@@ -4567,16 +4558,16 @@
         <v>77</v>
       </c>
       <c r="F75">
-        <v>30.43977</v>
+        <v>30.4329</v>
       </c>
       <c r="G75">
-        <v>-81.4081</v>
+        <v>-81.407</v>
       </c>
       <c r="H75">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J75" t="s">
         <v>109</v>
@@ -4585,16 +4576,16 @@
         <v>127</v>
       </c>
       <c r="O75" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P75" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q75" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R75" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="76" spans="1:18">
@@ -4605,43 +4596,40 @@
         <v>43137</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D76" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E76" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F76">
-        <v>30.4329</v>
+        <v>24.80786</v>
       </c>
       <c r="G76">
-        <v>-81.407</v>
+        <v>-80.83499999999999</v>
       </c>
       <c r="H76">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I76">
         <v>1</v>
       </c>
       <c r="J76" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="K76" t="s">
-        <v>127</v>
-      </c>
-      <c r="O76" t="s">
-        <v>227</v>
+        <v>124</v>
       </c>
       <c r="P76" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q76" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R76" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="77" spans="1:18">
@@ -4661,16 +4649,16 @@
         <v>78</v>
       </c>
       <c r="F77">
-        <v>24.80786</v>
+        <v>24.80772</v>
       </c>
       <c r="G77">
-        <v>-80.83499999999999</v>
+        <v>-80.8355</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J77" t="s">
         <v>94</v>
@@ -4679,13 +4667,13 @@
         <v>124</v>
       </c>
       <c r="P77" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q77" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R77" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="1:18">
@@ -4696,40 +4684,43 @@
         <v>43137</v>
       </c>
       <c r="C78" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D78" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E78" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F78">
-        <v>24.80772</v>
+        <v>27.17168</v>
       </c>
       <c r="G78">
-        <v>-80.8355</v>
+        <v>-80.1833</v>
       </c>
       <c r="H78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="K78" t="s">
-        <v>124</v>
+        <v>136</v>
+      </c>
+      <c r="N78" t="s">
+        <v>191</v>
       </c>
       <c r="P78" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q78" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R78" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:18">
@@ -4766,17 +4757,14 @@
       <c r="K79" t="s">
         <v>136</v>
       </c>
-      <c r="N79" t="s">
-        <v>192</v>
-      </c>
       <c r="P79" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q79" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R79" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:18">
@@ -4784,22 +4772,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="1">
-        <v>43137</v>
+        <v>43138</v>
       </c>
       <c r="C80" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D80" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E80" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F80">
-        <v>27.17168</v>
+        <v>25.85589</v>
       </c>
       <c r="G80">
-        <v>-80.1833</v>
+        <v>-81.68340000000001</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -4808,19 +4796,22 @@
         <v>1</v>
       </c>
       <c r="J80" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K80" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="N80" t="s">
+        <v>192</v>
       </c>
       <c r="P80" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q80" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R80" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="81" spans="1:18">
@@ -4861,13 +4852,13 @@
         <v>193</v>
       </c>
       <c r="P81" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q81" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R81" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="82" spans="1:18">
@@ -4908,13 +4899,13 @@
         <v>194</v>
       </c>
       <c r="P82" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q82" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R82" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="83" spans="1:18">
@@ -4955,13 +4946,13 @@
         <v>195</v>
       </c>
       <c r="P83" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q83" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R83" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="84" spans="1:18">
@@ -4990,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="I84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J84" t="s">
         <v>111</v>
@@ -4998,17 +4989,14 @@
       <c r="K84" t="s">
         <v>138</v>
       </c>
-      <c r="N84" t="s">
-        <v>196</v>
-      </c>
       <c r="P84" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q84" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R84" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="85" spans="1:18">
@@ -5016,43 +5004,40 @@
         <v>84</v>
       </c>
       <c r="B85" s="1">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="C85" t="s">
-        <v>27</v>
-      </c>
-      <c r="D85" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="E85" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F85">
-        <v>25.85589</v>
+        <v>27.43161</v>
       </c>
       <c r="G85">
-        <v>-81.68340000000001</v>
+        <v>-80.27630000000001</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J85" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K85" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P85" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q85" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R85" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" spans="1:18">
@@ -5069,16 +5054,16 @@
         <v>81</v>
       </c>
       <c r="F86">
-        <v>27.43161</v>
+        <v>27.43255</v>
       </c>
       <c r="G86">
-        <v>-80.27630000000001</v>
+        <v>-80.27670000000001</v>
       </c>
       <c r="H86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="s">
         <v>112</v>
@@ -5086,14 +5071,17 @@
       <c r="K86" t="s">
         <v>139</v>
       </c>
+      <c r="N86" t="s">
+        <v>196</v>
+      </c>
       <c r="P86" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q86" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R86" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="87" spans="1:18">
@@ -5101,43 +5089,46 @@
         <v>86</v>
       </c>
       <c r="B87" s="1">
-        <v>43139</v>
+        <v>43137</v>
       </c>
       <c r="C87" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="D87" t="s">
+        <v>46</v>
       </c>
       <c r="E87" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F87">
-        <v>27.43255</v>
+        <v>30.3858</v>
       </c>
       <c r="G87">
-        <v>-80.27670000000001</v>
+        <v>-86.8536</v>
       </c>
       <c r="H87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87">
         <v>1</v>
       </c>
       <c r="J87" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K87" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N87" t="s">
         <v>197</v>
       </c>
       <c r="P87" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q87" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R87" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="88" spans="1:18">
@@ -5145,46 +5136,49 @@
         <v>87</v>
       </c>
       <c r="B88" s="1">
-        <v>43137</v>
+        <v>43134</v>
       </c>
       <c r="C88" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D88" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E88" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F88">
-        <v>30.3858</v>
+        <v>27.6495</v>
       </c>
       <c r="G88">
-        <v>-86.8536</v>
+        <v>-82.7501</v>
       </c>
       <c r="H88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I88">
         <v>1</v>
       </c>
       <c r="J88" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K88" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N88" t="s">
         <v>198</v>
       </c>
+      <c r="O88" t="s">
+        <v>226</v>
+      </c>
       <c r="P88" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q88" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R88" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:18">
@@ -5213,7 +5207,7 @@
         <v>2</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J89" t="s">
         <v>114</v>
@@ -5221,20 +5215,17 @@
       <c r="K89" t="s">
         <v>141</v>
       </c>
-      <c r="N89" t="s">
-        <v>199</v>
-      </c>
       <c r="O89" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="P89" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q89" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R89" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="90" spans="1:18">
@@ -5245,43 +5236,46 @@
         <v>43134</v>
       </c>
       <c r="C90" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D90" t="s">
         <v>47</v>
       </c>
       <c r="E90" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F90">
-        <v>27.6495</v>
+        <v>27.6559</v>
       </c>
       <c r="G90">
-        <v>-82.7501</v>
+        <v>-82.7393</v>
       </c>
       <c r="H90">
         <v>2</v>
       </c>
       <c r="I90">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J90" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K90" t="s">
         <v>141</v>
       </c>
+      <c r="N90" t="s">
+        <v>199</v>
+      </c>
       <c r="O90" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P90" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q90" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R90" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="91" spans="1:18">
@@ -5318,20 +5312,17 @@
       <c r="K91" t="s">
         <v>141</v>
       </c>
-      <c r="N91" t="s">
-        <v>200</v>
-      </c>
       <c r="O91" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P91" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q91" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R91" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="92" spans="1:18">
@@ -5351,13 +5342,13 @@
         <v>84</v>
       </c>
       <c r="F92">
-        <v>27.6559</v>
+        <v>27.6501</v>
       </c>
       <c r="G92">
-        <v>-82.7393</v>
+        <v>-82.7347</v>
       </c>
       <c r="H92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -5368,17 +5359,20 @@
       <c r="K92" t="s">
         <v>141</v>
       </c>
+      <c r="N92" t="s">
+        <v>200</v>
+      </c>
       <c r="O92" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P92" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q92" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R92" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93" spans="1:18">
@@ -5407,7 +5401,7 @@
         <v>3</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J93" t="s">
         <v>115</v>
@@ -5415,20 +5409,17 @@
       <c r="K93" t="s">
         <v>141</v>
       </c>
-      <c r="N93" t="s">
-        <v>201</v>
-      </c>
       <c r="O93" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="P93" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q93" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R93" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="94" spans="1:18">
@@ -5436,7 +5427,7 @@
         <v>93</v>
       </c>
       <c r="B94" s="1">
-        <v>43134</v>
+        <v>43138</v>
       </c>
       <c r="C94" t="s">
         <v>38</v>
@@ -5445,37 +5436,37 @@
         <v>47</v>
       </c>
       <c r="E94" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F94">
-        <v>27.6501</v>
+        <v>29.63802</v>
       </c>
       <c r="G94">
-        <v>-82.7347</v>
+        <v>-85.148</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I94">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J94" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K94" t="s">
-        <v>141</v>
-      </c>
-      <c r="O94" t="s">
-        <v>229</v>
+        <v>142</v>
+      </c>
+      <c r="N94" t="s">
+        <v>201</v>
       </c>
       <c r="P94" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q94" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R94" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="1:18">
@@ -5512,17 +5503,14 @@
       <c r="K95" t="s">
         <v>142</v>
       </c>
-      <c r="N95" t="s">
-        <v>202</v>
-      </c>
       <c r="P95" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q95" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R95" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="96" spans="1:18">
@@ -5533,40 +5521,43 @@
         <v>43138</v>
       </c>
       <c r="C96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D96" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E96" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F96">
-        <v>29.63802</v>
+        <v>29.71343</v>
       </c>
       <c r="G96">
-        <v>-85.148</v>
+        <v>-84.7499</v>
       </c>
       <c r="H96">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I96">
         <v>1</v>
       </c>
       <c r="J96" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K96" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="N96" t="s">
+        <v>202</v>
       </c>
       <c r="P96" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q96" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R96" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:18">
@@ -5586,13 +5577,13 @@
         <v>86</v>
       </c>
       <c r="F97">
-        <v>29.71343</v>
+        <v>29.71624</v>
       </c>
       <c r="G97">
-        <v>-84.7499</v>
+        <v>-84.7466</v>
       </c>
       <c r="H97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -5603,17 +5594,14 @@
       <c r="K97" t="s">
         <v>143</v>
       </c>
-      <c r="N97" t="s">
-        <v>203</v>
-      </c>
       <c r="P97" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q97" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R97" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" spans="1:18">
@@ -5633,13 +5621,13 @@
         <v>86</v>
       </c>
       <c r="F98">
-        <v>29.71624</v>
+        <v>29.71831</v>
       </c>
       <c r="G98">
-        <v>-84.7466</v>
+        <v>-84.744</v>
       </c>
       <c r="H98">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I98">
         <v>1</v>
@@ -5650,14 +5638,17 @@
       <c r="K98" t="s">
         <v>143</v>
       </c>
+      <c r="N98" t="s">
+        <v>203</v>
+      </c>
       <c r="P98" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q98" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R98" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="99" spans="1:18">
@@ -5677,13 +5668,13 @@
         <v>86</v>
       </c>
       <c r="F99">
-        <v>29.71831</v>
+        <v>29.73627</v>
       </c>
       <c r="G99">
-        <v>-84.744</v>
+        <v>-84.7229</v>
       </c>
       <c r="H99">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I99">
         <v>1</v>
@@ -5698,13 +5689,13 @@
         <v>204</v>
       </c>
       <c r="P99" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q99" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R99" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="100" spans="1:18">
@@ -5724,13 +5715,13 @@
         <v>86</v>
       </c>
       <c r="F100">
-        <v>29.73627</v>
+        <v>29.7464</v>
       </c>
       <c r="G100">
-        <v>-84.7229</v>
+        <v>-84.7123</v>
       </c>
       <c r="H100">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I100">
         <v>1</v>
@@ -5745,13 +5736,13 @@
         <v>205</v>
       </c>
       <c r="P100" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q100" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R100" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="101" spans="1:18">
@@ -5792,13 +5783,13 @@
         <v>206</v>
       </c>
       <c r="P101" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q101" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R101" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:18">
@@ -5835,17 +5826,14 @@
       <c r="K102" t="s">
         <v>143</v>
       </c>
-      <c r="N102" t="s">
-        <v>207</v>
-      </c>
       <c r="P102" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q102" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R102" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:18">
@@ -5853,43 +5841,43 @@
         <v>102</v>
       </c>
       <c r="B103" s="1">
-        <v>43138</v>
+        <v>43133</v>
       </c>
       <c r="C103" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D103" t="s">
         <v>51</v>
       </c>
       <c r="E103" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F103">
-        <v>29.7464</v>
+        <v>28.13208</v>
       </c>
       <c r="G103">
-        <v>-84.7123</v>
+        <v>-82.8282</v>
       </c>
       <c r="H103">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I103">
         <v>1</v>
       </c>
       <c r="J103" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K103" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P103" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q103" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R103" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="104" spans="1:18">
@@ -5900,40 +5888,43 @@
         <v>43133</v>
       </c>
       <c r="C104" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D104" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E104" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F104">
-        <v>28.13208</v>
+        <v>28.11171</v>
       </c>
       <c r="G104">
-        <v>-82.8282</v>
+        <v>-82.837</v>
       </c>
       <c r="H104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104">
         <v>1</v>
       </c>
       <c r="J104" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K104" t="s">
-        <v>144</v>
+        <v>145</v>
+      </c>
+      <c r="N104" t="s">
+        <v>207</v>
       </c>
       <c r="P104" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q104" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R104" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:18">
@@ -5974,13 +5965,13 @@
         <v>208</v>
       </c>
       <c r="P105" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q105" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R105" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="106" spans="1:18">
@@ -6021,13 +6012,13 @@
         <v>209</v>
       </c>
       <c r="P106" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R106" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" spans="1:18">
@@ -6068,13 +6059,13 @@
         <v>210</v>
       </c>
       <c r="P107" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q107" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R107" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="108" spans="1:18">
@@ -6115,13 +6106,13 @@
         <v>211</v>
       </c>
       <c r="P108" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q108" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R108" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="109" spans="1:18">
@@ -6162,13 +6153,13 @@
         <v>212</v>
       </c>
       <c r="P109" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q109" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R109" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:18">
@@ -6209,13 +6200,13 @@
         <v>213</v>
       </c>
       <c r="P110" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q110" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R110" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="111" spans="1:18">
@@ -6244,7 +6235,7 @@
         <v>2</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J111" t="s">
         <v>119</v>
@@ -6252,17 +6243,14 @@
       <c r="K111" t="s">
         <v>145</v>
       </c>
-      <c r="N111" t="s">
-        <v>214</v>
-      </c>
       <c r="P111" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q111" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R111" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:18">
@@ -6273,40 +6261,46 @@
         <v>43133</v>
       </c>
       <c r="C112" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D112" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="E112" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F112">
-        <v>28.11171</v>
+        <v>30.06609</v>
       </c>
       <c r="G112">
-        <v>-82.837</v>
+        <v>-85.6161</v>
       </c>
       <c r="H112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J112" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s">
-        <v>145</v>
+        <v>121</v>
+      </c>
+      <c r="N112" t="s">
+        <v>214</v>
+      </c>
+      <c r="O112" t="s">
+        <v>228</v>
       </c>
       <c r="P112" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q112" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R112" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="113" spans="1:18">
@@ -6347,16 +6341,16 @@
         <v>215</v>
       </c>
       <c r="O113" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P113" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q113" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R113" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="114" spans="1:18">
@@ -6397,16 +6391,16 @@
         <v>216</v>
       </c>
       <c r="O114" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P114" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q114" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R114" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115" spans="1:18">
@@ -6447,16 +6441,16 @@
         <v>217</v>
       </c>
       <c r="O115" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P115" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q115" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R115" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="116" spans="1:18">
@@ -6493,20 +6487,17 @@
       <c r="K116" t="s">
         <v>121</v>
       </c>
-      <c r="N116" t="s">
-        <v>218</v>
-      </c>
       <c r="O116" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P116" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q116" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R116" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:18">
@@ -6526,13 +6517,13 @@
         <v>89</v>
       </c>
       <c r="F117">
-        <v>30.06609</v>
+        <v>30.08727</v>
       </c>
       <c r="G117">
-        <v>-85.6161</v>
+        <v>-85.6602</v>
       </c>
       <c r="H117">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I117">
         <v>1</v>
@@ -6543,17 +6534,20 @@
       <c r="K117" t="s">
         <v>121</v>
       </c>
+      <c r="N117" t="s">
+        <v>218</v>
+      </c>
       <c r="O117" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P117" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q117" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R117" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="118" spans="1:18">
@@ -6594,16 +6588,16 @@
         <v>219</v>
       </c>
       <c r="O118" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="P118" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q118" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R118" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" spans="1:18">
@@ -6611,96 +6605,46 @@
         <v>118</v>
       </c>
       <c r="B119" s="1">
-        <v>43133</v>
+        <v>43137</v>
       </c>
       <c r="C119" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D119" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E119" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F119">
-        <v>30.08727</v>
+        <v>29.30722</v>
       </c>
       <c r="G119">
-        <v>-85.6602</v>
+        <v>-81.0467</v>
       </c>
       <c r="H119">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="K119" t="s">
-        <v>121</v>
-      </c>
-      <c r="N119" t="s">
-        <v>220</v>
+        <v>146</v>
       </c>
       <c r="O119" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P119" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Q119" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R119" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18">
-      <c r="A120">
-        <v>119</v>
-      </c>
-      <c r="B120" s="1">
-        <v>43137</v>
-      </c>
-      <c r="C120" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120" t="s">
-        <v>47</v>
-      </c>
-      <c r="E120" t="s">
-        <v>90</v>
-      </c>
-      <c r="F120">
-        <v>29.30722</v>
-      </c>
-      <c r="G120">
-        <v>-81.0467</v>
-      </c>
-      <c r="H120">
-        <v>6</v>
-      </c>
-      <c r="I120">
-        <v>2</v>
-      </c>
-      <c r="J120" t="s">
-        <v>120</v>
-      </c>
-      <c r="K120" t="s">
-        <v>146</v>
-      </c>
-      <c r="O120" t="s">
-        <v>231</v>
-      </c>
-      <c r="P120" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q120" t="s">
-        <v>233</v>
-      </c>
-      <c r="R120" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
